--- a/docs/samples/orbit-sample.xlsx
+++ b/docs/samples/orbit-sample.xlsx
@@ -11,6 +11,9 @@
     <x:sheet name="Budget" sheetId="3" r:id="rId4"/>
     <x:sheet name="Resources" sheetId="4" r:id="rId5"/>
     <x:sheet name="RAID" sheetId="5" r:id="rId6"/>
+    <x:sheet name="ScopeWbs" sheetId="6" r:id="rId7"/>
+    <x:sheet name="TimeUsed" sheetId="7" r:id="rId8"/>
+    <x:sheet name="Decisions" sheetId="8" r:id="rId9"/>
   </x:sheets>
   <x:definedNames/>
   <x:calcPr calcId="125725"/>
@@ -423,6 +426,354 @@
   </x:si>
   <x:si>
     <x:t>Resolved</x:t>
+  </x:si>
+  <x:si>
+    <x:t>project_id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>wbs_code</x:t>
+  </x:si>
+  <x:si>
+    <x:t>parent_wbs</x:t>
+  </x:si>
+  <x:si>
+    <x:t>phase</x:t>
+  </x:si>
+  <x:si>
+    <x:t>task_name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>depends_on_wbs</x:t>
+  </x:si>
+  <x:si>
+    <x:t>is_deliverable</x:t>
+  </x:si>
+  <x:si>
+    <x:t>deliverable_doc_required</x:t>
+  </x:si>
+  <x:si>
+    <x:t>base_estimate_hours</x:t>
+  </x:si>
+  <x:si>
+    <x:t>percent_complete</x:t>
+  </x:si>
+  <x:si>
+    <x:t>status</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>No</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Discovery</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Discovery &amp; Requirements</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Yes</x:t>
+  </x:si>
+  <x:si>
+    <x:t>320</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Build</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Store POS Integration</x:t>
+  </x:si>
+  <x:si>
+    <x:t>900</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>E-commerce Replatform</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Rollout</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Rollout &amp; Hypercare</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.2;1.3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>400</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Analyse</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Source Data Profiling</x:t>
+  </x:si>
+  <x:si>
+    <x:t>240</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mapping &amp; Transformation</x:t>
+  </x:si>
+  <x:si>
+    <x:t>600</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cutover Rehearsal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>300</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cutover</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Production Cutover</x:t>
+  </x:si>
+  <x:si>
+    <x:t>180</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Assess</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Current-State Assessment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Plan</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opportunity Roadmap</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Conveyor &amp; Robotics Install</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1400</x:t>
+  </x:si>
+  <x:si>
+    <x:t>45</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WMS Integration</x:t>
+  </x:si>
+  <x:si>
+    <x:t>700</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PSD2/SCA Remediation</x:t>
+  </x:si>
+  <x:si>
+    <x:t>85</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Certify</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Audit &amp; Certification</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Data Catalogue</x:t>
+  </x:si>
+  <x:si>
+    <x:t>480</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Govern</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Policy &amp; Ownership</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35</x:t>
+  </x:si>
+  <x:si>
+    <x:t>resource_name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>week_starting</x:t>
+  </x:si>
+  <x:si>
+    <x:t>registered_hours</x:t>
+  </x:si>
+  <x:si>
+    <x:t>entry_type</x:t>
+  </x:si>
+  <x:si>
+    <x:t>notes</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-06-08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>38</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Work</x:t>
+  </x:si>
+  <x:si>
+    <x:t>POS adapter build</x:t>
+  </x:si>
+  <x:si>
+    <x:t>42</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Checkout UI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PM oversight</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Rehearsal prep - overtime</x:t>
+  </x:si>
+  <x:si>
+    <x:t>44</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Split with ORB-1001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Blocked day</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Holiday 2026-06-16 to 2026-06-27</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Commissioning</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SCA remediation</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Assessment write-up</x:t>
+  </x:si>
+  <x:si>
+    <x:t>decision_id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>owner</x:t>
+  </x:si>
+  <x:si>
+    <x:t>raised_date</x:t>
+  </x:si>
+  <x:si>
+    <x:t>needed_by</x:t>
+  </x:si>
+  <x:si>
+    <x:t>consequence_if_delayed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>D-1002-1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Approve revised go-live date (Aug 1)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Overdue</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Steering Committee</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-06-01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cutover cannot be scheduled; team idle and client SLA at risk</x:t>
+  </x:si>
+  <x:si>
+    <x:t>D-1002-2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Fund additional data-cleansing sprint</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Pending</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Client Sponsor</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-06-12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Integrity errors persist into production</x:t>
+  </x:si>
+  <x:si>
+    <x:t>D-1001-1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Choose caching approach for POS API limits</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-05-25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Rollout throughput remains capped</x:t>
+  </x:si>
+  <x:si>
+    <x:t>D-1005-1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Confirm external auditor firm</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-06-05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Certification milestone slips</x:t>
+  </x:si>
+  <x:si>
+    <x:t>D-1006-1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Approve data-ownership RACI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Approved</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-05-02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-06-30</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1849,4 +2200,1292 @@
   <x:headerFooter/>
   <x:tableParts count="0"/>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
+  <x:sheetPr>
+    <x:outlinePr summaryBelow="1" summaryRight="1"/>
+  </x:sheetPr>
+  <x:dimension ref="A1:K23"/>
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:sheetData>
+    <x:row r="1" spans="1:11">
+      <x:c r="A1" s="0" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="B1" s="0" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="C1" s="0" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="D1" s="0" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="E1" s="0" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="F1" s="0" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="G1" s="0" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="H1" s="0" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="I1" s="0" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="J1" s="0" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="K1" s="0" t="s">
+        <x:v>145</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:11">
+      <x:c r="A2" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B2" s="0" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="C2" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D2" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E2" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F2" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G2" s="0" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="H2" s="0" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="I2" s="0" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="J2" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K2" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:11">
+      <x:c r="A3" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B3" s="0" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="C3" s="0" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="D3" s="0" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="E3" s="0" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="F3" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G3" s="0" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="H3" s="0" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="I3" s="0" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="J3" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="K3" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:11">
+      <x:c r="A4" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="C4" s="0" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="D4" s="0" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="E4" s="0" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="F4" s="0" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="G4" s="0" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="H4" s="0" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="I4" s="0" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="J4" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="K4" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:11">
+      <x:c r="A5" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B5" s="0" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="C5" s="0" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="D5" s="0" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="E5" s="0" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="F5" s="0" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="G5" s="0" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="H5" s="0" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="I5" s="0" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="J5" s="0" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="K5" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:11">
+      <x:c r="A6" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B6" s="0" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="C6" s="0" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="D6" s="0" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="E6" s="0" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="F6" s="0" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="G6" s="0" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="H6" s="0" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="I6" s="0" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="J6" s="0" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="K6" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:11">
+      <x:c r="A7" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B7" s="0" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="C7" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D7" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E7" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="F7" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G7" s="0" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="H7" s="0" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="I7" s="0" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="J7" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K7" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:11">
+      <x:c r="A8" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B8" s="0" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="C8" s="0" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="D8" s="0" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="E8" s="0" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="F8" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G8" s="0" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="H8" s="0" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="I8" s="0" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="J8" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="K8" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:11">
+      <x:c r="A9" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B9" s="0" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="C9" s="0" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="D9" s="0" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="E9" s="0" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="F9" s="0" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="G9" s="0" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="H9" s="0" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="I9" s="0" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="J9" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="K9" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:11">
+      <x:c r="A10" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B10" s="0" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="C10" s="0" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="D10" s="0" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="E10" s="0" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="F10" s="0" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="G10" s="0" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="H10" s="0" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="I10" s="0" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="J10" s="0" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="K10" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:11">
+      <x:c r="A11" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B11" s="0" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="C11" s="0" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="D11" s="0" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="E11" s="0" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="F11" s="0" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="G11" s="0" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="H11" s="0" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="I11" s="0" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="J11" s="0" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="K11" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:11">
+      <x:c r="A12" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B12" s="0" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="C12" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D12" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E12" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="F12" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G12" s="0" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="H12" s="0" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="I12" s="0" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="J12" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="K12" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:11">
+      <x:c r="A13" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B13" s="0" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="C13" s="0" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="D13" s="0" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="E13" s="0" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="F13" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G13" s="0" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="H13" s="0" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="I13" s="0" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="J13" s="0" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="K13" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:11">
+      <x:c r="A14" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B14" s="0" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="C14" s="0" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="D14" s="0" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="E14" s="0" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="F14" s="0" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="G14" s="0" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="H14" s="0" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="I14" s="0" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="J14" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="K14" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:11">
+      <x:c r="A15" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B15" s="0" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="C15" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D15" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F15" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G15" s="0" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="H15" s="0" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="I15" s="0" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="J15" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="K15" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:11">
+      <x:c r="A16" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B16" s="0" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="C16" s="0" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="D16" s="0" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="E16" s="0" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="F16" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G16" s="0" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="H16" s="0" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="I16" s="0" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="J16" s="0" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="K16" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:11">
+      <x:c r="A17" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B17" s="0" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="C17" s="0" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="D17" s="0" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="E17" s="0" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="F17" s="0" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="G17" s="0" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="H17" s="0" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="I17" s="0" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="J17" s="0" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="K17" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:11">
+      <x:c r="A18" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B18" s="0" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="C18" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D18" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E18" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F18" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G18" s="0" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="H18" s="0" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="I18" s="0" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="J18" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="K18" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:11">
+      <x:c r="A19" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B19" s="0" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="C19" s="0" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="D19" s="0" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="E19" s="0" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="F19" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G19" s="0" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="H19" s="0" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="I19" s="0" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="J19" s="0" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="K19" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:11">
+      <x:c r="A20" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B20" s="0" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="C20" s="0" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="D20" s="0" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="E20" s="0" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="F20" s="0" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="G20" s="0" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="H20" s="0" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="I20" s="0" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="J20" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K20" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:11">
+      <x:c r="A21" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B21" s="0" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="C21" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D21" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E21" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F21" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G21" s="0" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="H21" s="0" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="I21" s="0" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="J21" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="K21" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:11">
+      <x:c r="A22" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B22" s="0" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="C22" s="0" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="D22" s="0" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="E22" s="0" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="F22" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G22" s="0" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="H22" s="0" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="I22" s="0" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="J22" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="K22" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:11">
+      <x:c r="A23" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B23" s="0" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="C23" s="0" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="D23" s="0" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="E23" s="0" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="F23" s="0" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="G23" s="0" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="H23" s="0" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="I23" s="0" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="J23" s="0" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="K23" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:headerFooter/>
+  <x:tableParts count="0"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
+  <x:sheetPr>
+    <x:outlinePr summaryBelow="1" summaryRight="1"/>
+  </x:sheetPr>
+  <x:dimension ref="A1:G12"/>
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:sheetData>
+    <x:row r="1" spans="1:7">
+      <x:c r="A1" s="0" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="B1" s="0" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="C1" s="0" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="D1" s="0" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="E1" s="0" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="F1" s="0" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="G1" s="0" t="s">
+        <x:v>201</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:7">
+      <x:c r="A2" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B2" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="C2" s="0" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="D2" s="0" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="E2" s="0" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="F2" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G2" s="0" t="s">
+        <x:v>205</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:7">
+      <x:c r="A3" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B3" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="C3" s="0" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="D3" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E3" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="F3" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G3" s="0" t="s">
+        <x:v>205</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:7">
+      <x:c r="A4" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="C4" s="0" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="D4" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E4" s="0" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="F4" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G4" s="0" t="s">
+        <x:v>207</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:7">
+      <x:c r="A5" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B5" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="C5" s="0" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="D5" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E5" s="0" t="s">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="F5" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G5" s="0" t="s">
+        <x:v>209</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:7">
+      <x:c r="A6" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B6" s="0" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="C6" s="0" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="D6" s="0" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="E6" s="0" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="F6" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G6" s="0" t="s">
+        <x:v>210</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:7">
+      <x:c r="A7" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B7" s="0" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="C7" s="0" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="D7" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E7" s="0" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="F7" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G7" s="0" t="s">
+        <x:v>210</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:7">
+      <x:c r="A8" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B8" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="C8" s="0" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="D8" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E8" s="0" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="F8" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G8" s="0" t="s">
+        <x:v>213</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:7">
+      <x:c r="A9" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B9" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="C9" s="0" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="D9" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E9" s="0" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="F9" s="0" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="G9" s="0" t="s">
+        <x:v>215</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:7">
+      <x:c r="A10" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B10" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="C10" s="0" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="D10" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E10" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="F10" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G10" s="0" t="s">
+        <x:v>216</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:7">
+      <x:c r="A11" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B11" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="C11" s="0" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="D11" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E11" s="0" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="F11" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G11" s="0" t="s">
+        <x:v>217</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:7">
+      <x:c r="A12" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B12" s="0" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="C12" s="0" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="D12" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E12" s="0" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="F12" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G12" s="0" t="s">
+        <x:v>219</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:headerFooter/>
+  <x:tableParts count="0"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
+  <x:sheetPr>
+    <x:outlinePr summaryBelow="1" summaryRight="1"/>
+  </x:sheetPr>
+  <x:dimension ref="A1:H6"/>
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:sheetData>
+    <x:row r="1" spans="1:8">
+      <x:c r="A1" s="0" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="B1" s="0" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="C1" s="0" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="D1" s="0" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="E1" s="0" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="F1" s="0" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="G1" s="0" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="H1" s="0" t="s">
+        <x:v>225</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:8">
+      <x:c r="A2" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B2" s="0" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="C2" s="0" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="D2" s="0" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="E2" s="0" t="s">
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="F2" s="0" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="G2" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="H2" s="0" t="s">
+        <x:v>231</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:8">
+      <x:c r="A3" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B3" s="0" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="C3" s="0" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="D3" s="0" t="s">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="E3" s="0" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="F3" s="0" t="s">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="G3" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="H3" s="0" t="s">
+        <x:v>237</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:8">
+      <x:c r="A4" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="C4" s="0" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="D4" s="0" t="s">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="E4" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="F4" s="0" t="s">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="G4" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="H4" s="0" t="s">
+        <x:v>241</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:8">
+      <x:c r="A5" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B5" s="0" t="s">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="C5" s="0" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="D5" s="0" t="s">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="E5" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="F5" s="0" t="s">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="G5" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="H5" s="0" t="s">
+        <x:v>245</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:8">
+      <x:c r="A6" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B6" s="0" t="s">
+        <x:v>246</x:v>
+      </x:c>
+      <x:c r="C6" s="0" t="s">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="D6" s="0" t="s">
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="E6" s="0" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="F6" s="0" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="G6" s="0" t="s">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="H6" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:headerFooter/>
+  <x:tableParts count="0"/>
+</x:worksheet>
 </file>